--- a/04_Features/modules/loso_refit/c_data/loso_refit.xlsx
+++ b/04_Features/modules/loso_refit/c_data/loso_refit.xlsx
@@ -58,34 +58,34 @@
     <t xml:space="preserve">modules</t>
   </si>
   <si>
+    <t xml:space="preserve">T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d_mcsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">enet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lasso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">plain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rf</t>
+  </si>
+  <si>
     <t xml:space="preserve">acute</t>
   </si>
   <si>
-    <t xml:space="preserve">d_mcsa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">enet</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lasso</t>
-  </si>
-  <si>
     <t xml:space="preserve">ridge</t>
   </si>
   <si>
     <t xml:space="preserve">svm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">plain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rf</t>
   </si>
   <si>
     <t xml:space="preserve">total</t>
@@ -535,7 +535,7 @@
         <v>16</v>
       </c>
       <c r="F2" t="n">
-        <v>0.444504844977317</v>
+        <v>0.0701252400887916</v>
       </c>
       <c r="G2" t="n">
         <v>-0.14795918367347</v>
@@ -544,13 +544,13 @@
         <v>-0.14795918367347</v>
       </c>
       <c r="I2" t="n">
-        <v>0.81592039800995</v>
+        <v>0.805970149253731</v>
       </c>
       <c r="J2" t="n">
-        <v>0.592464028650787</v>
+        <v>0.218084423762261</v>
       </c>
       <c r="K2" t="n">
-        <v>0.592464028650787</v>
+        <v>0.218084423762261</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -573,7 +573,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="n">
-        <v>0.462372213177816</v>
+        <v>0.177100266471497</v>
       </c>
       <c r="G3" t="n">
         <v>-0.14795918367347</v>
@@ -582,13 +582,13 @@
         <v>-0.14795918367347</v>
       </c>
       <c r="I3" t="n">
-        <v>0.810945273631841</v>
+        <v>0.800995024875622</v>
       </c>
       <c r="J3" t="n">
-        <v>0.610331396851286</v>
+        <v>0.325059450144967</v>
       </c>
       <c r="K3" t="n">
-        <v>0.610331396851286</v>
+        <v>0.325059450144967</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -602,34 +602,34 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>0.395420724337231</v>
+        <v>0.140992211958394</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.242597386943361</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.210171391206952</v>
       </c>
       <c r="I4" t="n">
-        <v>0.810945273631841</v>
+        <v>0.208955223880597</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5433799080107</v>
+        <v>0.351163603165347</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5433799080107</v>
+        <v>0.383589598901755</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.0324259957364086</v>
       </c>
     </row>
     <row r="5">
@@ -640,34 +640,34 @@
         <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" t="n">
-        <v>0.381321799187095</v>
+        <v>0.249482477508396</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4556329596711</v>
+        <v>-0.392547898540062</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.428200529604371</v>
+        <v>-0.341990759105408</v>
       </c>
       <c r="I5" t="n">
-        <v>0.492537313432836</v>
+        <v>0.557213930348259</v>
       </c>
       <c r="J5" t="n">
-        <v>0.809522328791466</v>
+        <v>0.591473236613804</v>
       </c>
       <c r="K5" t="n">
-        <v>0.836954758858194</v>
+        <v>0.642030376048458</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0274324300667288</v>
+        <v>-0.0505571394346542</v>
       </c>
     </row>
     <row r="6">
@@ -678,7 +678,7 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -687,7 +687,7 @@
         <v>16</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0701252400887916</v>
+        <v>0.444504844977317</v>
       </c>
       <c r="G6" t="n">
         <v>-0.14795918367347</v>
@@ -696,13 +696,13 @@
         <v>-0.14795918367347</v>
       </c>
       <c r="I6" t="n">
-        <v>0.805970149253731</v>
+        <v>0.81592039800995</v>
       </c>
       <c r="J6" t="n">
-        <v>0.218084423762261</v>
+        <v>0.592464028650787</v>
       </c>
       <c r="K6" t="n">
-        <v>0.218084423762261</v>
+        <v>0.592464028650787</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -716,7 +716,7 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
@@ -725,7 +725,7 @@
         <v>17</v>
       </c>
       <c r="F7" t="n">
-        <v>0.177100266471497</v>
+        <v>0.462372213177816</v>
       </c>
       <c r="G7" t="n">
         <v>-0.14795918367347</v>
@@ -734,13 +734,13 @@
         <v>-0.14795918367347</v>
       </c>
       <c r="I7" t="n">
-        <v>0.800995024875622</v>
+        <v>0.810945273631841</v>
       </c>
       <c r="J7" t="n">
-        <v>0.325059450144967</v>
+        <v>0.610331396851286</v>
       </c>
       <c r="K7" t="n">
-        <v>0.325059450144967</v>
+        <v>0.610331396851286</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -763,25 +763,25 @@
         <v>22</v>
       </c>
       <c r="F8" t="n">
-        <v>0.140992211958394</v>
+        <v>0.395420724337231</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.242597386943361</v>
+        <v>-0.14795918367347</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.210171391206952</v>
+        <v>-0.14795918367347</v>
       </c>
       <c r="I8" t="n">
-        <v>0.208955223880597</v>
+        <v>0.810945273631841</v>
       </c>
       <c r="J8" t="n">
-        <v>0.351163603165347</v>
+        <v>0.5433799080107</v>
       </c>
       <c r="K8" t="n">
-        <v>0.383589598901755</v>
+        <v>0.5433799080107</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0324259957364086</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -801,25 +801,25 @@
         <v>23</v>
       </c>
       <c r="F9" t="n">
-        <v>0.249482477508396</v>
+        <v>0.381321799187095</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.392547898540062</v>
+        <v>-0.4556329596711</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.341990759105408</v>
+        <v>-0.428200529604371</v>
       </c>
       <c r="I9" t="n">
-        <v>0.557213930348259</v>
+        <v>0.492537313432836</v>
       </c>
       <c r="J9" t="n">
-        <v>0.591473236613804</v>
+        <v>0.809522328791466</v>
       </c>
       <c r="K9" t="n">
-        <v>0.642030376048458</v>
+        <v>0.836954758858194</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0505571394346542</v>
+        <v>-0.0274324300667288</v>
       </c>
     </row>
     <row r="10">
@@ -836,7 +836,7 @@
         <v>15</v>
       </c>
       <c r="E10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F10" t="n">
         <v>0.392983399454889</v>
@@ -950,7 +950,7 @@
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F13" t="n">
         <v>0.37156217891133</v>
